--- a/test_doc/new_org/syllabus_7_it.xlsx
+++ b/test_doc/new_org/syllabus_7_it.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Computer Systems Revisited</t>
+          <t>Word Processing Basics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hardware and software</t>
+          <t>Creating a document</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -461,26 +461,26 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Input-process-output</t>
+          <t>Formatting text</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Advanced Word Processing</t>
+          <t>Email and Communication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tables and images</t>
+          <t>Writing an email</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,22 +491,22 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Page layout</t>
+          <t>Netiquette</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spreadsheets</t>
+          <t>Spreadsheets Basics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Formulas and functions</t>
+          <t>Rows, columns and cells</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sorting and filtering</t>
+          <t>Simple formulas</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -531,16 +531,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Charts and Graphs</t>
+          <t>Advanced Word Processing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Making charts</t>
+          <t>Tables and images</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -551,22 +551,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Choosing the right chart</t>
+          <t>Page layout</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Presentations That Work</t>
+          <t>Presentations</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Slide design</t>
+          <t>Creating slides</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -574,33 +574,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Term 2</t>
+          <t>Term 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Presenting to the class</t>
+          <t>Presenting ideas</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Introduction to Coding</t>
+          <t>Internet Research Skills</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Block coding basics</t>
+          <t>Finding reliable information</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,22 +611,22 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Making a small game</t>
+          <t>Citing sources</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Internet Research Skills</t>
+          <t>Being Safe Online</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Finding reliable information</t>
+          <t>Passwords and privacy</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citing sources</t>
+          <t>Cyber etiquette</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -651,16 +651,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Email and Communication</t>
+          <t>Typing Practice</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Writing an email</t>
+          <t>Home row practice</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -671,41 +671,11 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Netiquette</t>
+          <t>Speed building</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cyber Safety</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Strong passwords</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Term 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Recognising scams</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
